--- a/mau-google-sheet-diem.xlsx
+++ b/mau-google-sheet-diem.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B3FE4"/>
-        <bgColor rgb="007B3FE4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,52 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="90" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Thời gian</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Tên học sinh</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Điểm</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tên</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tên bài</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Phần</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Số điểm</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tổng số câu</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Phần trăm</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Chi tiết theo nhóm (JSON)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chi tiết bài làm (JSON)</t>
         </is>
       </c>
     </row>
@@ -486,24 +459,21 @@
           <t>Nguyễn Văn A</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bài 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ghép thanh mẫu</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>15</v>
-      </c>
-      <c r="E2" t="n">
-        <v>80</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>{"bpmf": {"correct": 5, "total": 6}, "dtnl": {"correct": 4, "total": 5}, "gkh": {"correct": 3, "total": 4}}</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[{"id": "s005", "hanzi": "包", "type": "initial", "hint": "āo", "correct": "bāo", "selected": "bāo", "isCorrect": true}, {"id": "s005", "hanzi": "包", "type": "tone", "hint": "bao", "correct": "bāo", "selected": "báo", "isCorrect": false}]</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -517,24 +487,21 @@
           <t>Trần Thị B</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bài 1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ghép vận mẫu</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>9</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>15</v>
-      </c>
-      <c r="E3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>{"bpmf": {"correct": 3, "total": 5}, "dtnl": {"correct": 3, "total": 5}, "gkh": {"correct": 3, "total": 5}}</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[{"id": "s060", "hanzi": "高", "type": "initial", "hint": "āo", "correct": "gāo", "selected": "kāo", "isCorrect": false}]</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/mau-google-sheet-diem.xlsx
+++ b/mau-google-sheet-diem.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,20 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Lớp</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Tên bài</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Phần</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Số điểm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Tổng số câu</t>
         </is>
@@ -451,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16 10:30:00</t>
+          <t>2026-08-16 10-30-00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,25 +466,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>6A1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Bài 1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Ghép thanh mẫu</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>12</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16 10:35:00</t>
+          <t>2026-08-16 10-35-00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -489,18 +499,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>6A2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Bài 1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Ghép vận mẫu</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>9</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>15</v>
       </c>
     </row>

--- a/mau-google-sheet-diem.xlsx
+++ b/mau-google-sheet-diem.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16 10-30-00</t>
+          <t>2026-08-16 10:30:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16 10-35-00</t>
+          <t>2026-08-16 10:35:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/mau-google-sheet-diem.xlsx
+++ b/mau-google-sheet-diem.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Thời gian</t>
+          <t>Thời gian bắt đầu</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -450,13 +450,23 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>Tổng số câu</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Thời gian kết thúc</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Tổng thời gian (phút)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16 10:30:00</t>
+          <t>2026-08-16 10:25:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,12 +494,20 @@
       </c>
       <c r="G2" t="n">
         <v>15</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:30:00</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16 10:35:00</t>
+          <t>2026-08-16 10:31:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,6 +535,14 @@
       </c>
       <c r="G3" t="n">
         <v>15</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:35:00</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
